--- a/data/excel/Autommerce_Partners_Lebanon.xlsx
+++ b/data/excel/Autommerce_Partners_Lebanon.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1102,12 +1102,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>ACONVERTS</t>
+          <t>Hovi Digital Lab</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://aconverts.com</t>
+          <t>https://thehovi.com</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1124,17 +1124,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Almoe</t>
+          <t>Microbits</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://almoe.co</t>
+          <t>https://microbits.co</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1146,17 +1146,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Maze</t>
+          <t>Plennix Technologies</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://wearemaze.com</t>
+          <t>https://plennix.com</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1168,39 +1168,39 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Creators Specialist</t>
+          <t>ERP Cloud</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://creatorsspecialist.com</t>
+          <t>https://erpcloudllc.com</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>IY Media</t>
+          <t>AddBloom</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://iy.media</t>
+          <t>https://addbloom.com</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>GrowthArc</t>
+          <t>ACONVERTS</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://growtharc.agency</t>
+          <t>https://aconverts.com</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1234,17 +1234,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Nobrand Agency</t>
+          <t>Almoe</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://nobrandagency.com</t>
+          <t>https://almoe.co</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1256,61 +1256,61 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Weave Wider</t>
+          <t>Maze</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://weavewider.com</t>
+          <t>https://wearemaze.com</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>NavyBits</t>
+          <t>Creators Specialist</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://navybits.com</t>
+          <t>https://creatorsspecialist.com</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>EDM</t>
+          <t>IY Media</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://edm-tech.com</t>
+          <t>https://iy.media</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1322,39 +1322,39 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Oxit</t>
+          <t>GrowthArc</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://oxitlb.com</t>
+          <t>https://growtharc.agency</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SEIDOR</t>
+          <t>Nobrand Agency</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://seidor.com</t>
+          <t>https://nobrandagency.com</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -1366,39 +1366,39 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Eastline Digital</t>
+          <t>Weave Wider</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://eastlinemarketing.com</t>
+          <t>https://weavewider.com</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Elite Information Tech</t>
+          <t>NavyBits</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://eliteinformationtech.com</t>
+          <t>https://navybits.com</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -1410,17 +1410,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Adperical</t>
+          <t>EDM</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://adperical.com</t>
+          <t>https://edm-tech.com</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -1432,27 +1432,137 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>Oxit</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>https://oxitlb.com</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce System Integration Companies</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>SEIDOR</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>https://seidor.com</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce System Integration Companies</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Eastline Digital</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>https://eastlinemarketing.com</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Elite Information Tech</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>https://eliteinformationtech.com</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Adperical</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>https://adperical.com</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>Megatek</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>https://megatekgroup.com</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D46"/>
+  <autoFilter ref="A1:D51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_Lebanon.xlsx
+++ b/data/excel/Autommerce_Partners_Lebanon.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1561,8 +1561,52 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Web Synergy</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>https://websynergy.tech</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Nothing Concepts</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>https://nothingconcepts.com</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Website Development Agencies</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D51"/>
+  <autoFilter ref="A1:D53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_Lebanon.xlsx
+++ b/data/excel/Autommerce_Partners_Lebanon.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision makers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Company details'!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision makers'!$A$1:$G$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +30,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +68,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,19 +435,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
@@ -458,6 +470,21 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Product Fit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -482,6 +509,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>info@koein.com; ksa@koein.com; sales@koein.com; uae@koein.com; usa@koein.com</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>+961 70 890 978; +961 1 613 049; +961 1 482 525; +961 1 489 494; +1 832 583 3090; +1 216 327 5256</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/koein</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -504,6 +546,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>info@eurisko.net</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eurisko</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -526,6 +579,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>info@borninteractive.com</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/born-interactive</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -548,6 +612,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>info@tedmob.com</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>+961 4 545 466</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tedmob</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -570,6 +649,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>info@thewebaddicts.com</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>+961 70 444 309; +961 1 485 075; +971 50 782 3363</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/thewebaddicts</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -592,6 +686,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/astound-digital</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -614,6 +715,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emooduniverse</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -636,6 +744,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>+961 1 495 670</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/spearheadagency</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -658,6 +777,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>hello@emaginelb.com</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>+961 76 348 097</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emaginelb</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -680,6 +814,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>info@aphcom.com</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>+961 79 438 108</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aphcom</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -702,6 +851,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>biz@krishtechnolabs.com</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>+1 306 631 0667; +1 913 206 0077; +44 20 3769 4814; +61 2 7255 0505; +91 75750 25646; +971 54 334 1033</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/krish-technolabs</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -724,6 +888,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>info@webneoo.com</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/webneoo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -746,6 +921,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>info@digitalits.com</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>+961 5 464 323; +961 71 080 840; +961 5 463 553</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/digitalits</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -768,6 +958,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>info@circosoft.net; info@circosoft.ae</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>+961 81 825 170; +971 50 795 0310; +961 79 157 318</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/circosoft</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -790,6 +995,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>info@luminacommerce.com</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>+971 56 842 6687</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/luminacommerce</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -812,6 +1032,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>hello@lateliergrowth.com</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>+961 71 725 632</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/l-atelier-growth</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -834,6 +1069,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>info@adchiefs.com</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>+961 71 787 351</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/adchiefs</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -856,6 +1106,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>info@nascode.com</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>+961 1 485 494; +961 76 664 222; +961 76 664 111; +1 832 425 2420</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nascode</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -878,6 +1143,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>info@wztechno.com</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>+961 70 646 348</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wztechno</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -900,6 +1180,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>info@loumi-x.com</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/loumi-x</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -922,6 +1213,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>info@gomema.com</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>+961 81 067 000; +357 96 999 917</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mema-trade-online-services-ltd</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -944,6 +1250,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>info@azka.tech</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>+961 70 504 898; +961 21 429 226; +971 50 228 6440</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/azkatech</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -966,6 +1287,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>rabihdib@gmail.com</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>+961 71 890 689</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -988,6 +1320,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>info@intouchmena.com</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>(+961) 3 068 545; (+974) 4434 1021; +966 56 642 5310; +971 50 146 8450</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intouch-mena</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1010,6 +1357,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>info@bybloshorizon.com</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>+33 7 60 47 33 65</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/byblos-horizon</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1032,6 +1394,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>contact@ustartup.co</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>+961 70 360 040; +961 76 360 040</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1054,6 +1427,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>info@wecansync.com; infolb@wecansync.com; infobr@wecansync.com; infocy@wecansync.com; infous@wecansync.com</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>+961 81 377 309; +1 202 379 5311; +1 352 216 1906; +357 96 055 587; +55 11 99637 6968</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wecansync</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1076,6 +1464,17 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>+961 1 426 489</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fittdesign</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1098,6 +1497,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>info@coperon.com</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>+961 1 487 485</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/coperon-technologies</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1120,6 +1534,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>rayan@thehovi.com</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>+971 52 100 0917</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1142,6 +1567,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>web@microbits.me</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>+961 25 953 401; +961 25 953 402; +971 4 383 5356; +971 50 851 0961; +966 55 914 6786; +41 78 934 0513; +44 7706 236262</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/microbits</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1164,6 +1604,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>info@plennix.com; sales.uae@plennix.com; sales.ksa@plennix.com; sales.lebanon@plennix.com; sales.egypt@plennix.com</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>+971 56 284 8969; +971 56 680 8951; +961 1 502 008; +961 71 559 054; +20 122 955 5509; +20 2 2269 2826</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/plennixtech</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1186,6 +1641,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>info@erpcloudllc.com</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>+1 438 875 3474; +961 5 459 982; +961 71 339 673; +966 12 603 3336</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/erp-cloud-llc</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1208,6 +1678,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>hello@addbloom.com; info@addbloom.com</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/addbloom</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1230,6 +1711,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aconverts</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1252,6 +1740,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1274,6 +1765,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>hello@wearemaze.com</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>+961 9 919 019</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wearemaze</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1296,6 +1802,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>info@creatorsspecialist.com</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>+961 71 996 032; +961 76 375 997</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/creators-specialist</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1318,6 +1839,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>ceo@iy.media; info@iy.media</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>+961 3 474 713; +961 76 358 133</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/iymedia</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1340,6 +1876,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>mortada.ib99@gmail.com</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1362,6 +1905,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>badeeh@nobrandholding.com; nb@nobrandholding.com</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nobrand-worldwide</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1384,6 +1938,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>hello@weavewider.com</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>+964 787 808 8666; +974 5103 9745</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/weavewider</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1406,6 +1975,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>info@navybits.com; sales@navybits.com</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>+961 81 920 075; +961 6 616 922</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/navybits</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1428,6 +2012,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>info@edm-tech.com; softsales@edm.com.lb</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>+961 1 307 907</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/engineering-design-&amp;-manufacturing</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1450,6 +2049,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>contact@oxitlb.com</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>+961 70 784 441</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oxitlb</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1472,6 +2086,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/seidor</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1494,6 +2115,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>info@eastlinemarketing.com</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>+961 3 989 816; +971 55 122 0947</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/eastline-digital</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1516,6 +2152,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>info@eliteinformationtech.com</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>+91 93512 73546</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/elite-information-tech</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1538,6 +2189,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>info@adperical.com</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>+961 1 956 448; +961 71 163 732</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1560,6 +2222,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>info@megateklb.com; info@megatekllc.com; info@implemea.com</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>+1 954 305 9375; +961 3 700 088; +967 670 1111</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/megatekgroup</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1582,6 +2259,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>info@websynergy.tech</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>+961 76 142 805; +961 71 763 262</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/websynergylb</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1604,9 +2296,1841 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>hello@nothingconcepts.com</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nothingconcepts</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D53"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Nagib Abdelnour</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nagib-abdelnour-a1b8b1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>CTO and Founding Partner</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Koein</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://koein.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Serge Jouljian</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/serge-jouljian-84b51486</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Koein</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://koein.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Walid Wannous</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wwannous</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder, Board, VP Experience Design</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Koein</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://koein.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Edgard Hanna Tawk</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/edgard-hanna-tawk-b3940b13</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Eurisko</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://eurisko.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mohammad Assi</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mohammad-assi-1205b519</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Head of Business Services</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Eurisko</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://eurisko.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Ziad Tawk</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ziadtawk</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CTO</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Eurisko</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://eurisko.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Amer Tabbara</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amertabbara</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Director, KSA</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Born Interactive</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://borninteractive.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Fadi Sabbagha</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fadisabbagha</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Born Interactive</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://borninteractive.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Haytham Sawma</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/haythamsawma</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Born Interactive</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://borninteractive.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Mario Hachem</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mariohachem</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>TEDMOB</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://tedmob.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Paula Jabbour</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paula-jabbour-1652b420a</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Manager</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>TEDMOB</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://tedmob.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Perla Smath</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/perla-smath-1a24aa163</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Marketing Manager</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TEDMOB</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://tedmob.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Assaad Abou Harb</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/assaadharb</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and Owner</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The Web Addicts</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://thewebaddicts.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Carol Karam</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/carol-karam-24718bb8</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Manager</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>The Web Addicts</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://thewebaddicts.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Andrea Allen</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aferrario</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Global Alliance Leader</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Astound Commerce</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://astoundcommerce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Igor Gorin</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/igorgorin</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Founder, Board Member and Strategy Advisor</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Astound Commerce</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://astoundcommerce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Jillian Baez</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jillian-baez-29328536</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Marketing and Alliance Partnerships Manager</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Astound Commerce</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://astoundcommerce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Waad Nakad Matanick</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/waad-nakad-matanick-74984217</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Global Director of Marketing</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Astound Commerce</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://astoundcommerce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>William Donlan</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/william-donlan</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Astound Commerce</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://astoundcommerce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Bernadette Saliba</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bernadette-saliba-75588a27</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>e-mood</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://e-mood.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Farah N. Bader</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/farahbader</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Regional Partner</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Spearhead Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://spearheadagency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Katia Abou-Rizk Barakat</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/katia-abou-rizk</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Partner, Strategy and Planning</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Spearhead Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://spearheadagency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Wadih Antoun</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/wantoun</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and Partner</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Spearhead Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://spearheadagency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Kass-Hanna</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/patrickkasshanna</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Emagine</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://emaginelb.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Peter Saad</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/peter-saad-9a9033135</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>AphCom</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://aphcom.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Jiten Padmashali</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jitenpadmashali</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Managing Director</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Krish Technolabs</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://krishtechnolabs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Nishit Kathlana</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nishitkathlana</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Global Strategic Alliances Manager</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Krish Technolabs</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://krishtechnolabs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Celine Khourieh</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/celine-khourieh-43a94852</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Webneoo</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://webneoo.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Mazen El Hajj</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mazen-el-hajj-1a124121b</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Founder</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Circosoft</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://circosoft.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Nora Nassar</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nora-nassar-267a05127</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Circosoft</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://circosoft.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Garen Mehranian</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/garen-mehranian</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>LUMINA</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://luminacommerce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Daniel Badaoui</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-badaoui</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>L'Atelier Growth</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://lateliergrowth.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Nazih Al-Bardan</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr"/>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nazih-al-bardan-974405294</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>AdChiefs</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://adchiefs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Nader Stouhi</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/naderstouhi</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Nascode</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://nascode.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Mark Mehanna</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mark-mehanna-48765034</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>MEMA Ecommerce Development</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://mema.agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Rabih Dib</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>+961 71 890 689</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>rabihdib@gmail.com</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rabihdib</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>RD Digital Agency (Rabih Dib)</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://rabihdib.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Elie Sawma</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eliesawma</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>General Manager, KSA</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Georges Abla</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgesabla</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Territory Manager, Lebanon</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Mark Sawma</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Vany Sawma</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vanysawma</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Head of Growth</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Victor D. Sawma</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/victorsawma</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CTO</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>intouch</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://intouchmena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Shadi Adada</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shadi-adada-9b3179185</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>FittDesign</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://fittdesign.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Ramzy Dib</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ramzydib</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Microbits</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://microbits.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Antonio Alhaber</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonio-alhaber-89731323a</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Plennix Technologies</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://plennix.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Samer Hobeika</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/samer-hobeika-48077890</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Plennix Technologies</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://plennix.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Ali Atwi</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>ali.atwi@erpxcloud.com</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Business Owner</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>ERP Cloud</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://erpcloudllc.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Ziad Nassar</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ziadsnassar</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>AddBloom</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://addbloom.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Alex Chidiac</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexxchidiac</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>ACONVERTS</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://aconverts.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Tanios Abi Saad</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/taniosabisaad</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Creators Specialist</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://creatorsspecialist.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Ibrahim Younes</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>IY Media</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://iy.media</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Mortada</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>mortada.ib99@gmail.com</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>GrowthArc</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://growtharc.agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Ali Rida</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr"/>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Weave Wider</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://weavewider.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Hassan Tabbal</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hassantabbal</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>NavyBits</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://navybits.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Abdussamii Al-Sharif</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdussamii-al-sharif-3a526821</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://edm-tech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Elie Rizkallah</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elie-michel-rizkallah</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Regional Head of Sales</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://edm-tech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Imad Kozem</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/imad-kozem-00ab7219</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://edm-tech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Zuhdi Al Ahwal</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/zuhdi-al-ahwal-3919743</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>EDM</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://edm-tech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Sergi Biosca Arpa</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sergibiosca</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SEIDOR</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://seidor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Sílvia Sousa Cristòfol</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/silvia-sousa-cristofol</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Chief Strategy and Transformation Officer</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>SEIDOR</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://seidor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Sobhi Shayckha</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr"/>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Web Synergy</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://websynergy.tech</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Andre Zourob</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>Nothing Concepts</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://nothingconcepts.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G62"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>